--- a/requirement_3_physical_product/test_cases_summary.xlsx
+++ b/requirement_3_physical_product/test_cases_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HCMUS\HK3_2025\SoftwareTesting\HW\HW1\requirement_3_physical_product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E4BDD9-F194-4BB6-8CF4-4D7524F92E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2A871E-748C-4491-AB27-478611F5E470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="188">
   <si>
     <t>Mã TC</t>
   </si>
@@ -387,9 +387,6 @@
     <t>Có ảnh thiết bị và thẻ sinh viên trong cùng khung hình</t>
   </si>
   <si>
-    <t>Done</t>
-  </si>
-  <si>
     <t>Lưu trong `device_photo/`</t>
   </si>
   <si>
@@ -630,56 +627,7 @@
     <t>Open</t>
   </si>
   <si>
-    <t>Defect Details</t>
-  </si>
-  <si>
-    <t>DEF-01 – Quạt phát ra tiếng cọt kẹt lớn khi đứng yên ở tốc độ 3</t>
-  </si>
-  <si>
-    <t>Related Test Cases: TC-03, TC-09</t>
-  </si>
-  <si>
-    <t>Defect Type: Mechanical noise / Abnormal noise</t>
-  </si>
-  <si>
-    <t>Severity: Medium</t>
-  </si>
-  <si>
-    <t>Priority: Medium</t>
-  </si>
-  <si>
-    <t>Status: Open</t>
-  </si>
-  <si>
-    <t>Mô tả lỗi:
-Khi quạt được đặt đứng yên, không bật chức năng quay trái phải, quạt phát ra tiếng cọt kẹt khá lớn ở tốc độ 3. Khi chuyển về tốc độ 1, tiếng cọt kẹt giảm rõ rệt. Lỗi này không làm quạt dừng hoạt động nhưng ảnh hưởng đến trải nghiệm sử dụng và có thể cho thấy vấn đề cơ khí, motor, trục quay hoặc lồng/cánh quạt bị rung/cạ nhẹ.</t>
-  </si>
-  <si>
-    <t>Steps to Reproduce:
-1. Đặt quạt trên nền phẳng.
-2. Đảm bảo chức năng quay trái phải đang tắt.
-3. Bật quạt ở tốc độ 3.
-4. Lắng nghe tiếng motor/cánh/lồng quạt trong khoảng 10–20 giây.
-5. Chuyển về tốc độ 1 và so sánh tiếng cọt kẹt.</t>
-  </si>
-  <si>
-    <t>Expected Result:
-Quạt chạy ổn định ở các mức tốc độ, tiếng ồn thay đổi theo tốc độ nhưng không có tiếng cọt kẹt lớn hoặc âm thanh cơ khí bất thường.</t>
-  </si>
-  <si>
-    <t>Actual Result:
-Khi quạt đứng yên ở tốc độ 3, xuất hiện tiếng cọt kẹt lớn. Khi chuyển về tốc độ 1, tiếng cọt kẹt giảm rõ rệt.</t>
-  </si>
-  <si>
-    <t>Impact:
-Ảnh hưởng đến trải nghiệm sử dụng, đặc biệt trong không gian yên tĩnh. Nếu tiếng cọt kẹt đến từ bộ phận cơ khí, trục quay hoặc lồng/cánh quạt bị cạ, lỗi có thể ảnh hưởng đến độ bền lâu dài của thiết bị.</t>
-  </si>
-  <si>
-    <t>Suggested Fix / Recommendation:
-Kiểm tra lại lồng quạt, cánh quạt, trục quay, khớp motor và các ốc cố định. Siết lại các bộ phận bị lỏng nếu có. Nếu tiếng cọt kẹt vẫn còn, nên đem quạt đi kiểm tra hoặc bảo trì.</t>
-  </si>
-  <si>
-    <t>Kết quả kiểm thử cho thấy quạt lửng ASIA A16007-XV0 hoạt động ổn định ở hầu hết các chức năng cơ bản như bật/tắt, chuyển tốc độ, quay trái phải, an toàn lồng quạt, dây điện và chạy liên tục. Tuy nhiên, trong quá trình kiểm thử phát hiện một defect chính: quạt phát ra tiếng cọt kẹt lớn khi đứng yên ở tốc độ 3. Defect này ảnh hưởng đến TC-03 và TC-09, được đánh giá severity Medium và đã được log thành GitHub Issue DEF-01.</t>
+    <t>Hoàn thành</t>
   </si>
 </sst>
 </file>
@@ -750,7 +698,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -767,6 +715,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,7 +1019,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="55" customWidth="1"/>
@@ -1078,7 +1027,7 @@
     <col min="8" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1107,7 +1056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1136,7 +1085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1165,7 +1114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -1194,7 +1143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -1223,7 +1172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1252,7 +1201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
@@ -1281,7 +1230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
@@ -1310,7 +1259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>55</v>
       </c>
@@ -1339,7 +1288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
@@ -1368,7 +1317,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>67</v>
       </c>
@@ -1397,7 +1346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>73</v>
       </c>
@@ -1426,7 +1375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>79</v>
       </c>
@@ -1455,7 +1404,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>85</v>
       </c>
@@ -1484,7 +1433,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>91</v>
       </c>
@@ -1513,7 +1462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>97</v>
       </c>
@@ -1550,14 +1499,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="57.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
@@ -1568,169 +1517,169 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="B12" s="2" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1741,16 +1690,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1758,151 +1707,151 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1910,9 +1859,9 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1920,103 +1869,103 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2024,9 +1973,9 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2034,47 +1983,47 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2082,137 +2031,111 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>189</v>
-      </c>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>190</v>
-      </c>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>191</v>
-      </c>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>192</v>
-      </c>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>193</v>
-      </c>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>194</v>
-      </c>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>195</v>
-      </c>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>196</v>
-      </c>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>197</v>
-      </c>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>198</v>
-      </c>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>199</v>
-      </c>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>200</v>
-      </c>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2220,20 +2143,16 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>201</v>
-      </c>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
